--- a/data/trans_orig/P79A4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A4_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>849</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
